--- a/tabtools/demo/demo_puttab.xlsx
+++ b/tabtools/demo/demo_puttab.xlsx
@@ -315,7 +315,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="16">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -325,27 +325,13 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="12"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
       <name val="Arial"/>
     </font>
     <font>
@@ -353,41 +339,18 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <b/>
-      <name val="Arial"/>
-    </font>
-    <font>
+      <i/>
       <sz val="8"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <i/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -401,15 +364,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDBE5F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -419,220 +384,102 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium"/>
       <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -660,247 +507,247 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="13" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="14" t="s">
+      <c r="K4" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="14" t="s">
+      <c r="D5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="I6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="15" t="s">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="I7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -924,206 +771,206 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="23" t="s">
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="27" t="s">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="14" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="20" t="s">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="11" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="31" t="s">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="A5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="11" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="31" t="s">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="12" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="11" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="31" t="s">
+      <c r="A8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="12" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="20" t="s">
+      <c r="A9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="E9" s="11" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="31" t="s">
+      <c r="A10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="20" t="s">
+      <c r="A11" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="28" t="s">
+      <c r="E11" s="11" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="33" t="s">
+      <c r="A12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D12" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="13" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1147,87 +994,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="36" t="s">
+      <c r="A2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="19" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="37" t="s">
+      <c r="A4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="20" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="41" t="s">
+      <c r="C5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_puttab.xlsx
+++ b/tabtools/demo/demo_puttab.xlsx
@@ -374,7 +374,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -384,6 +384,27 @@
     </border>
     <border/>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -392,7 +413,28 @@
     </border>
     <border>
       <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -415,7 +457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -424,13 +466,28 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -442,7 +499,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -451,10 +508,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -466,16 +523,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -507,37 +564,37 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="7" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -545,34 +602,34 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="10" t="s">
         <v>40</v>
       </c>
     </row>
@@ -580,34 +637,34 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -615,34 +672,34 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -650,34 +707,34 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="D5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -685,34 +742,34 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="6" t="s">
         <v>41</v>
       </c>
     </row>
@@ -720,34 +777,34 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="8" t="s">
         <v>41</v>
       </c>
     </row>
@@ -771,206 +828,206 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="15" t="s">
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="20" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="E2" s="19" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="16" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="16" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="17" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="16" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="A8" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="17" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="9" t="s">
+      <c r="A10" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="17" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="11" t="s">
+      <c r="E11" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="D12" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="18" t="s">
         <v>84</v>
       </c>
     </row>
@@ -994,87 +1051,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="22" t="s">
+      <c r="B1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="27" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="21" t="s">
+      <c r="A2" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="C2" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="26" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="24" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="18" t="s">
+      <c r="A4" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="D4" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="25" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="s">
+      <c r="A5" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="16" t="s">
+      <c r="C5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>1</v>
       </c>
     </row>

--- a/tabtools/demo/demo_puttab.xlsx
+++ b/tabtools/demo/demo_puttab.xlsx
@@ -9,13 +9,16 @@
     <sheet name="Matrix" sheetId="1" r:id="rId2"/>
     <sheet name="Frame" sheetId="2" r:id="rId4"/>
     <sheet name="Collapse" sheetId="3" r:id="rId5"/>
+    <sheet name="Stacked Tables" sheetId="4" r:id="rId6"/>
+    <sheet name="Panels" sheetId="5" r:id="rId7"/>
+    <sheet name="Spans" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="162" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="254" uniqueCount="136">
   <si>
     <t>Table P1. OLS Coefficients for Car Price</t>
   </si>
@@ -309,6 +312,120 @@
   </si>
   <si>
     <t>52</t>
+  </si>
+  <si>
+    <t>Table P4. Two Tables Stacked in One Source</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>Repair</t>
+  </si>
+  <si>
+    <t>Good (4-5)</t>
+  </si>
+  <si>
+    <t>Poor (1-3)</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>6,072</t>
+  </si>
+  <si>
+    <t>6,385</t>
+  </si>
+  <si>
+    <t>6,013</t>
+  </si>
+  <si>
+    <t>6,118</t>
+  </si>
+  <si>
+    <t>Table P5. Panels with Their Own Headers</t>
+  </si>
+  <si>
+    <t>A. Relapses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Under 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   55 and over</t>
+  </si>
+  <si>
+    <t>B. New MRI activity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Repleted</t>
+  </si>
+  <si>
+    <t>Counts are crude.</t>
+  </si>
+  <si>
+    <t>Ratios are adjusted.</t>
+  </si>
+  <si>
+    <t>Relapses</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Scans</t>
+  </si>
+  <si>
+    <t>Person-years</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>280</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Table P6. A Spanning Header</t>
+  </si>
+  <si>
+    <t>Age group</t>
+  </si>
+  <si>
+    <t>Under 55</t>
+  </si>
+  <si>
+    <t>55 and over</t>
+  </si>
+  <si>
+    <t>Repleted</t>
+  </si>
+  <si>
+    <t>Counts</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Exposure</t>
   </si>
 </sst>
 </file>
@@ -374,7 +491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -453,11 +570,32 @@
       <bottom style="medium"/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -517,22 +655,91 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1051,75 +1258,75 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="27" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="26" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="24" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="22" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="5" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="23" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="23" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="21" t="s">
@@ -1141,4 +1348,385 @@
     <mergeCell ref="B5:E5"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="8.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="32" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="10.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B10:D10"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="8.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="10.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="49" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/tabtools/demo/demo_puttab.xlsx
+++ b/tabtools/demo/demo_puttab.xlsx
@@ -1472,7 +1472,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
-    <col min="2" max="2" width="16.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="21.7109375" style="1" customWidth="true"/>
     <col min="3" max="3" width="10.7109375" style="1" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" style="1" customWidth="true"/>
   </cols>
@@ -1618,10 +1618,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B6:D6"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="B10:D10"/>
   </mergeCells>
